--- a/AMS/019-Kent-Height-CHS/KENT HEIGHTS FY_25-26_Provisional_V4.xlsx
+++ b/AMS/019-Kent-Height-CHS/KENT HEIGHTS FY_25-26_Provisional_V4.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\BHARAT\2025-2026\BCB\AMS\019-Kent-Height-CHS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72BFFCB5-0CF3-4D44-870B-C9BBFEE714EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9C51AD3-993B-4403-ADB9-0681768775BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="724" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="724" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BS" sheetId="2" r:id="rId1"/>
@@ -933,9 +933,6 @@
     <t xml:space="preserve"> Interest Accrued        24-25</t>
   </si>
   <si>
-    <t xml:space="preserve"> Interest Accrued        25-26</t>
-  </si>
-  <si>
     <t xml:space="preserve">  Receivable from Members as on 31-03-2026</t>
   </si>
   <si>
@@ -1411,6 +1408,9 @@
   </si>
   <si>
     <t>Add: Property Tax Payable write Off</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Interest Accrued   2025-26</t>
   </si>
 </sst>
 </file>
@@ -3115,37 +3115,37 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="36" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -3997,7 +3997,7 @@
         <v>0</v>
       </c>
       <c r="B27" s="69" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C27" s="32">
         <f>42256+91829</f>
@@ -4222,7 +4222,7 @@
         <v>0</v>
       </c>
       <c r="B38" s="272" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="C38" s="87">
         <v>6756</v>
@@ -4274,7 +4274,7 @@
         <v>0</v>
       </c>
       <c r="B40" s="274" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="C40" s="17">
         <f>-IE!H55</f>
@@ -4396,7 +4396,7 @@
       <c r="D45" s="200"/>
       <c r="E45" s="201"/>
       <c r="F45" s="312" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="G45" s="312"/>
       <c r="H45" s="313"/>
@@ -4426,7 +4426,7 @@
     </row>
     <row r="48" spans="1:19" s="210" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A48" s="205" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="B48" s="206"/>
       <c r="C48" s="207"/>
@@ -4448,7 +4448,7 @@
     </row>
     <row r="49" spans="1:19" s="78" customFormat="1" ht="9.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A49" s="211" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="B49" s="206"/>
       <c r="C49" s="207"/>
@@ -4461,14 +4461,14 @@
     </row>
     <row r="50" spans="1:19" s="78" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A50" s="211" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="B50" s="206"/>
       <c r="C50" s="207"/>
       <c r="D50" s="200"/>
       <c r="E50" s="201"/>
       <c r="F50" s="314" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="G50" s="314"/>
       <c r="H50" s="315"/>
@@ -4694,7 +4694,7 @@
         <v>0</v>
       </c>
       <c r="B10" s="60" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C10" s="108"/>
       <c r="D10" s="286">
@@ -4849,7 +4849,7 @@
         <v>0</v>
       </c>
       <c r="F17" s="60" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="G17" s="154">
         <v>24000</v>
@@ -5064,7 +5064,7 @@
     <row r="28" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A28" s="65"/>
       <c r="B28" s="83" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C28" s="154">
         <v>1125000</v>
@@ -5106,7 +5106,7 @@
         <v>0</v>
       </c>
       <c r="F30" s="112" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="G30" s="109">
         <v>1092000</v>
@@ -5124,7 +5124,7 @@
         <v>0</v>
       </c>
       <c r="F31" s="112" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="G31" s="109">
         <v>-1092000</v>
@@ -5500,7 +5500,7 @@
         <v>0</v>
       </c>
       <c r="B53" s="60" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C53" s="17"/>
       <c r="D53" s="290">
@@ -5538,7 +5538,7 @@
         <v>0</v>
       </c>
       <c r="F55" s="156" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="G55" s="157"/>
       <c r="H55" s="158">
@@ -5630,7 +5630,7 @@
       <c r="D60" s="200"/>
       <c r="E60" s="201"/>
       <c r="F60" s="312" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="G60" s="312"/>
       <c r="H60" s="313"/>
@@ -5660,7 +5660,7 @@
     </row>
     <row r="63" spans="1:12" s="210" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A63" s="205" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="B63" s="206"/>
       <c r="C63" s="207"/>
@@ -5682,7 +5682,7 @@
     </row>
     <row r="64" spans="1:12" s="78" customFormat="1" ht="9.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A64" s="211" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="B64" s="206"/>
       <c r="C64" s="207"/>
@@ -5695,14 +5695,14 @@
     </row>
     <row r="65" spans="1:10" s="78" customFormat="1" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A65" s="211" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="B65" s="206"/>
       <c r="C65" s="207"/>
       <c r="D65" s="200"/>
       <c r="E65" s="201"/>
       <c r="F65" s="314" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="G65" s="314"/>
       <c r="H65" s="315"/>
@@ -5763,21 +5763,24 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:N23"/>
   <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="5.5546875" style="4" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="15.5546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.44140625" style="12" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.77734375" style="12" customWidth="1"/>
     <col min="4" max="4" width="10.44140625" style="4" customWidth="1"/>
     <col min="5" max="5" width="8.33203125" style="12" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13" style="12" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13" style="12" hidden="1" customWidth="1"/>
     <col min="7" max="7" width="11.33203125" style="12" customWidth="1"/>
-    <col min="8" max="8" width="14.88671875" style="12" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="17.33203125" style="12" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="19.88671875" style="12" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.6640625" style="12" customWidth="1"/>
+    <col min="9" max="9" width="11.5546875" style="12" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.77734375" style="12" customWidth="1"/>
     <col min="11" max="11" width="9.6640625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.77734375" customWidth="1"/>
     <col min="13" max="13" width="7.33203125" style="4" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -5852,7 +5855,7 @@
         <v>293</v>
       </c>
       <c r="G4" s="132" t="s">
-        <v>294</v>
+        <v>453</v>
       </c>
       <c r="H4" s="132" t="s">
         <v>113</v>
@@ -5923,7 +5926,7 @@
         <v>6.8500000000000005E-2</v>
       </c>
       <c r="N6" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
     </row>
     <row r="7" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
@@ -5971,7 +5974,7 @@
         <v>6.8500000000000005E-2</v>
       </c>
       <c r="N7" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="8" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
@@ -6019,7 +6022,7 @@
         <v>6.8500000000000005E-2</v>
       </c>
       <c r="N8" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="9" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
@@ -6067,7 +6070,7 @@
         <v>6.8500000000000005E-2</v>
       </c>
       <c r="N9" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="10" spans="1:14" ht="16.95" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
@@ -6075,7 +6078,7 @@
         <v>4</v>
       </c>
       <c r="B10" s="134" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C10" s="138">
         <v>1188767</v>
@@ -6102,12 +6105,12 @@
         <v>1193530</v>
       </c>
       <c r="K10" s="8" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="L10" s="2"/>
       <c r="M10" s="137"/>
       <c r="N10" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="11" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
@@ -6151,7 +6154,7 @@
         <v>6.8500000000000005E-2</v>
       </c>
       <c r="N11" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="12" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
@@ -6197,7 +6200,7 @@
         <v>6.8500000000000005E-2</v>
       </c>
       <c r="N12" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="13" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
@@ -6243,7 +6246,7 @@
         <v>6.8500000000000005E-2</v>
       </c>
       <c r="N13" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="14" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
@@ -6289,7 +6292,7 @@
         <v>6.8500000000000005E-2</v>
       </c>
       <c r="N14" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
     <row r="15" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
@@ -6297,7 +6300,7 @@
         <v>7</v>
       </c>
       <c r="B15" s="134" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C15" s="138">
         <v>1131665</v>
@@ -6333,7 +6336,7 @@
         <v>6.8500000000000005E-2</v>
       </c>
       <c r="N15" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="16" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
@@ -6341,7 +6344,7 @@
         <v>8</v>
       </c>
       <c r="B16" s="134" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C16" s="138">
         <v>1131665</v>
@@ -6377,7 +6380,7 @@
         <v>6.8500000000000005E-2</v>
       </c>
       <c r="N16" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="17" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
@@ -6425,7 +6428,7 @@
         <v>6.8500000000000005E-2</v>
       </c>
       <c r="N17" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="18" spans="1:14" hidden="1" x14ac:dyDescent="0.3">
@@ -6438,12 +6441,12 @@
       <c r="I18" s="3"/>
       <c r="J18" s="3"/>
     </row>
-    <row r="19" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="8">
         <v>1</v>
       </c>
       <c r="B19" s="134" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="C19" s="2">
         <v>7805844</v>
@@ -6474,19 +6477,19 @@
         <v>8033197</v>
       </c>
       <c r="K19" s="8" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="L19" s="2">
-        <v>0</v>
+        <v>8306685</v>
       </c>
       <c r="M19" s="137"/>
     </row>
-    <row r="20" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="8">
         <v>2</v>
       </c>
       <c r="B20" s="134" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C20" s="2">
         <v>1188767</v>
@@ -6517,19 +6520,19 @@
         <v>1223391</v>
       </c>
       <c r="K20" s="8" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="L20" s="2">
-        <v>0</v>
+        <v>1265041</v>
       </c>
       <c r="M20" s="137"/>
     </row>
-    <row r="21" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="8">
         <v>3</v>
       </c>
       <c r="B21" s="134" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C21" s="2">
         <v>1188767</v>
@@ -6560,19 +6563,19 @@
         <v>1223391</v>
       </c>
       <c r="K21" s="8" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="L21" s="2">
-        <v>0</v>
+        <v>1265041</v>
       </c>
       <c r="M21" s="137"/>
     </row>
-    <row r="22" spans="1:14" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:14" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="8">
         <v>4</v>
       </c>
       <c r="B22" s="134" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C22" s="2">
         <v>1131665</v>
@@ -6603,14 +6606,14 @@
         <v>1189808</v>
       </c>
       <c r="K22" s="8" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="L22" s="2">
-        <v>0</v>
+        <v>1210008</v>
       </c>
       <c r="M22" s="137"/>
     </row>
-    <row r="23" spans="1:14" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:14" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A23" s="217"/>
       <c r="B23" s="218" t="s">
         <v>217</v>
@@ -6647,7 +6650,7 @@
       <c r="K23" s="220"/>
       <c r="L23" s="219">
         <f>SUM(L19:L22)</f>
-        <v>0</v>
+        <v>12046775</v>
       </c>
       <c r="M23" s="217"/>
     </row>
@@ -6658,8 +6661,8 @@
     <mergeCell ref="A2:M2"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
-  <pageMargins left="0.31496062992125984" right="0.31496062992125984" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
-  <pageSetup paperSize="9" scale="80" orientation="landscape" r:id="rId1"/>
+  <pageMargins left="0.39370078740157483" right="0.31496062992125984" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
+  <pageSetup paperSize="9" scale="71" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -6697,7 +6700,7 @@
     </row>
     <row r="3" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A3" s="335" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B3" s="335"/>
       <c r="C3" s="335"/>
@@ -6714,10 +6717,10 @@
         <v>93</v>
       </c>
       <c r="D4" s="223" t="s">
+        <v>443</v>
+      </c>
+      <c r="E4" s="223" t="s">
         <v>444</v>
-      </c>
-      <c r="E4" s="223" t="s">
-        <v>445</v>
       </c>
       <c r="F4" s="224" t="s">
         <v>7</v>
@@ -6731,7 +6734,7 @@
         <v>101</v>
       </c>
       <c r="C5" s="221" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="D5" s="222">
         <v>21096</v>
@@ -7057,7 +7060,7 @@
       <c r="A20" s="172"/>
       <c r="B20" s="173"/>
       <c r="C20" s="126" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="D20" s="187">
         <f>'Major Rep. Chgs'!K94</f>
@@ -7101,7 +7104,7 @@
     </row>
     <row r="24" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A24" s="343" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B24" s="343"/>
       <c r="C24" s="343"/>
@@ -7126,7 +7129,7 @@
         <v>1</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>190</v>
@@ -7140,7 +7143,7 @@
         <v>2</v>
       </c>
       <c r="B27" s="8" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>38</v>
@@ -7154,7 +7157,7 @@
         <v>3</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>187</v>
@@ -7210,7 +7213,7 @@
         <v>7</v>
       </c>
       <c r="B32" s="180" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>199</v>
@@ -7247,7 +7250,7 @@
     </row>
     <row r="36" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A36" s="342" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B36" s="342"/>
       <c r="C36" s="342"/>
@@ -7289,7 +7292,7 @@
         <v>401</v>
       </c>
       <c r="C39" s="25" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="D39" s="48">
         <v>50000</v>
@@ -7403,7 +7406,7 @@
         <v>1403</v>
       </c>
       <c r="C47" s="25" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="D47" s="20">
         <v>200000</v>
@@ -7417,7 +7420,7 @@
         <v>2304</v>
       </c>
       <c r="C48" s="25" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="D48" s="20">
         <v>100000</v>
@@ -7470,31 +7473,31 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:8" ht="18" x14ac:dyDescent="0.3">
-      <c r="B1" s="351" t="str">
+      <c r="B1" s="349" t="str">
         <f>'Sch - G FA'!B1</f>
         <v>KENT - HEIGHTS CO-OPERATIVE HOUSING SOCIETY LTD.</v>
       </c>
-      <c r="C1" s="351"/>
-      <c r="D1" s="351"/>
-      <c r="E1" s="351"/>
-      <c r="F1" s="351"/>
-      <c r="G1" s="351"/>
-      <c r="H1" s="351"/>
+      <c r="C1" s="349"/>
+      <c r="D1" s="349"/>
+      <c r="E1" s="349"/>
+      <c r="F1" s="349"/>
+      <c r="G1" s="349"/>
+      <c r="H1" s="349"/>
     </row>
     <row r="2" spans="2:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B2" s="348" t="s">
+      <c r="B2" s="346" t="s">
         <v>97</v>
       </c>
-      <c r="C2" s="348"/>
-      <c r="D2" s="348"/>
-      <c r="E2" s="348"/>
-      <c r="F2" s="348"/>
-      <c r="G2" s="348"/>
-      <c r="H2" s="348"/>
+      <c r="C2" s="346"/>
+      <c r="D2" s="346"/>
+      <c r="E2" s="346"/>
+      <c r="F2" s="346"/>
+      <c r="G2" s="346"/>
+      <c r="H2" s="346"/>
     </row>
     <row r="3" spans="2:8" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B3" s="342" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C3" s="342"/>
       <c r="D3" s="342"/>
@@ -7504,27 +7507,27 @@
       <c r="H3" s="342"/>
     </row>
     <row r="4" spans="2:8" ht="37.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="355" t="s">
+      <c r="B4" s="353" t="s">
         <v>46</v>
       </c>
-      <c r="C4" s="353" t="s">
+      <c r="C4" s="351" t="s">
+        <v>298</v>
+      </c>
+      <c r="D4" s="350" t="s">
+        <v>125</v>
+      </c>
+      <c r="E4" s="350"/>
+      <c r="F4" s="350"/>
+      <c r="G4" s="351" t="s">
+        <v>126</v>
+      </c>
+      <c r="H4" s="351" t="s">
         <v>299</v>
       </c>
-      <c r="D4" s="352" t="s">
-        <v>125</v>
-      </c>
-      <c r="E4" s="352"/>
-      <c r="F4" s="352"/>
-      <c r="G4" s="353" t="s">
-        <v>126</v>
-      </c>
-      <c r="H4" s="353" t="s">
-        <v>300</v>
-      </c>
     </row>
     <row r="5" spans="2:8" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B5" s="356"/>
-      <c r="C5" s="354"/>
+      <c r="B5" s="354"/>
+      <c r="C5" s="352"/>
       <c r="D5" s="124" t="s">
         <v>127</v>
       </c>
@@ -7534,8 +7537,8 @@
       <c r="F5" s="124" t="s">
         <v>128</v>
       </c>
-      <c r="G5" s="354"/>
-      <c r="H5" s="354"/>
+      <c r="G5" s="352"/>
+      <c r="H5" s="352"/>
     </row>
     <row r="6" spans="2:8" ht="30" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
       <c r="B6" s="241" t="s">
@@ -7678,11 +7681,11 @@
       <c r="H12" s="202"/>
     </row>
     <row r="13" spans="2:8" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B13" s="348" t="s">
+      <c r="B13" s="346" t="s">
         <v>129</v>
       </c>
-      <c r="C13" s="348"/>
-      <c r="D13" s="348"/>
+      <c r="C13" s="346"/>
+      <c r="D13" s="346"/>
       <c r="E13" s="184"/>
       <c r="F13" s="184"/>
       <c r="G13" s="184"/>
@@ -7690,7 +7693,7 @@
     </row>
     <row r="14" spans="2:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B14" s="342" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="C14" s="342"/>
       <c r="D14" s="342"/>
@@ -7700,10 +7703,10 @@
       <c r="H14" s="183"/>
     </row>
     <row r="15" spans="2:8" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B15" s="349" t="s">
+      <c r="B15" s="347" t="s">
         <v>37</v>
       </c>
-      <c r="C15" s="350"/>
+      <c r="C15" s="348"/>
       <c r="D15" s="227" t="s">
         <v>95</v>
       </c>
@@ -7728,7 +7731,7 @@
     </row>
     <row r="18" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B18" s="244" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="C18" s="231"/>
       <c r="D18" s="232">
@@ -7746,7 +7749,7 @@
     </row>
     <row r="20" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B20" s="245" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C20" s="233"/>
       <c r="D20" s="234">
@@ -7763,10 +7766,10 @@
       </c>
     </row>
     <row r="22" spans="2:4" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B22" s="346" t="s">
+      <c r="B22" s="355" t="s">
         <v>237</v>
       </c>
-      <c r="C22" s="347"/>
+      <c r="C22" s="356"/>
       <c r="D22" s="235">
         <f>SUM(D16:D21)</f>
         <v>369036</v>
@@ -7781,10 +7784,10 @@
       <c r="D24" s="312"/>
     </row>
     <row r="25" spans="2:4" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B25" s="349" t="s">
+      <c r="B25" s="347" t="s">
         <v>37</v>
       </c>
-      <c r="C25" s="350"/>
+      <c r="C25" s="348"/>
       <c r="D25" s="227" t="s">
         <v>95</v>
       </c>
@@ -7800,7 +7803,7 @@
     </row>
     <row r="27" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B27" s="244" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="C27" s="231"/>
       <c r="D27" s="225">
@@ -7809,7 +7812,7 @@
     </row>
     <row r="28" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B28" s="244" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="C28" s="231"/>
       <c r="D28" s="225">
@@ -7827,7 +7830,7 @@
     </row>
     <row r="30" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B30" s="244" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="C30" s="231"/>
       <c r="D30" s="225">
@@ -7845,7 +7848,7 @@
     </row>
     <row r="32" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B32" s="245" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C32" s="233"/>
       <c r="D32" s="226">
@@ -7863,7 +7866,7 @@
     </row>
     <row r="34" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B34" s="246" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="C34" s="236"/>
       <c r="D34" s="237">
@@ -7871,10 +7874,10 @@
       </c>
     </row>
     <row r="35" spans="2:4" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B35" s="346" t="s">
+      <c r="B35" s="355" t="s">
         <v>238</v>
       </c>
-      <c r="C35" s="347"/>
+      <c r="C35" s="356"/>
       <c r="D35" s="238">
         <f>SUM(D26:D34)</f>
         <v>521658</v>
@@ -7885,10 +7888,10 @@
       <c r="D36" s="240"/>
     </row>
     <row r="37" spans="2:4" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B37" s="346" t="s">
+      <c r="B37" s="355" t="s">
         <v>239</v>
       </c>
-      <c r="C37" s="347"/>
+      <c r="C37" s="356"/>
       <c r="D37" s="238">
         <f>+D22+D35</f>
         <v>890694</v>
@@ -7897,6 +7900,11 @@
     <row r="38" spans="2:4" ht="15" thickTop="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="16">
+    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="B35:C35"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="B14:D14"/>
+    <mergeCell ref="B24:D24"/>
     <mergeCell ref="B13:D13"/>
     <mergeCell ref="B25:C25"/>
     <mergeCell ref="B1:H1"/>
@@ -7908,11 +7916,6 @@
     <mergeCell ref="B4:B5"/>
     <mergeCell ref="H4:H5"/>
     <mergeCell ref="G4:G5"/>
-    <mergeCell ref="B37:C37"/>
-    <mergeCell ref="B35:C35"/>
-    <mergeCell ref="B22:C22"/>
-    <mergeCell ref="B14:D14"/>
-    <mergeCell ref="B24:D24"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.39370078740157483" right="0.31496062992125984" top="0.59055118110236227" bottom="0.35433070866141736" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -7972,7 +7975,7 @@
     </row>
     <row r="3" spans="2:12" ht="16.2" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B3" s="358" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C3" s="358"/>
       <c r="D3" s="358"/>
@@ -7991,22 +7994,22 @@
         <v>50</v>
       </c>
       <c r="D4" s="128" t="s">
+        <v>302</v>
+      </c>
+      <c r="E4" s="128" t="s">
         <v>303</v>
       </c>
-      <c r="E4" s="128" t="s">
+      <c r="F4" s="128" t="s">
         <v>304</v>
       </c>
-      <c r="F4" s="128" t="s">
+      <c r="G4" s="128" t="s">
         <v>305</v>
-      </c>
-      <c r="G4" s="128" t="s">
-        <v>306</v>
       </c>
       <c r="H4" s="128" t="s">
         <v>51</v>
       </c>
       <c r="I4" s="129" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="J4" s="124" t="s">
         <v>52</v>
@@ -8324,7 +8327,7 @@
       <c r="B15" s="360" t="s">
         <v>7</v>
       </c>
-      <c r="C15" s="350"/>
+      <c r="C15" s="348"/>
       <c r="D15" s="253">
         <f t="shared" ref="D15:I15" si="11">SUM(D5:D14)</f>
         <v>114661910</v>
@@ -8384,49 +8387,49 @@
   <sheetData>
     <row r="1" spans="1:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A1" s="363" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="B1" s="364"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="365" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B2" s="366"/>
       <c r="D2" s="136" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="E2" s="136" t="s">
         <v>248</v>
       </c>
       <c r="F2" s="136" t="s">
+        <v>381</v>
+      </c>
+      <c r="G2" s="136" t="s">
         <v>382</v>
-      </c>
-      <c r="G2" s="136" t="s">
-        <v>383</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="72"/>
       <c r="B3" s="145" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="E3" s="151">
         <v>41783</v>
       </c>
       <c r="F3" s="152" t="s">
+        <v>384</v>
+      </c>
+      <c r="G3" s="1" t="s">
         <v>385</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>386</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="72" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B4" s="146">
         <v>890014.17</v>
@@ -8441,7 +8444,7 @@
         <v>866372</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
@@ -8457,12 +8460,12 @@
         <v>866372</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="72" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="B6" s="146">
         <f>E6</f>
@@ -8481,7 +8484,7 @@
     </row>
     <row r="8" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A8" s="72" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B8" s="147">
         <f>B4-B6</f>
@@ -8494,19 +8497,19 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="361" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="B10" s="362"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="72"/>
       <c r="B11" s="145" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="72" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B12" s="148">
         <v>4760</v>
@@ -8522,7 +8525,7 @@
     </row>
     <row r="14" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="72" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B14" s="149">
         <f>B12</f>
@@ -8541,19 +8544,19 @@
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" s="361" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B17" s="362"/>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" s="72"/>
       <c r="B18" s="145" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" s="72" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B19" s="148">
         <v>0</v>
@@ -8565,14 +8568,14 @@
     </row>
     <row r="21" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A21" s="72" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B21" s="149">
         <f>B19</f>
         <v>0</v>
       </c>
       <c r="C21" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="15" thickTop="1" x14ac:dyDescent="0.3">
@@ -8618,7 +8621,7 @@
       </c>
       <c r="K3" s="7"/>
       <c r="L3" s="30" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.3">
@@ -8639,7 +8642,7 @@
       </c>
       <c r="K4" s="7"/>
       <c r="L4" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="O4" s="159">
         <f>IE!H22</f>
@@ -8662,7 +8665,7 @@
       </c>
       <c r="K5" s="7"/>
       <c r="L5" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="O5" s="159">
         <f>IE!G23</f>
@@ -8689,7 +8692,7 @@
       </c>
       <c r="K6" s="7"/>
       <c r="L6" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="O6" s="159">
         <v>0</v>
@@ -8698,7 +8701,7 @@
     <row r="7" spans="1:15" x14ac:dyDescent="0.3">
       <c r="K7" s="7"/>
       <c r="L7" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="O7" s="160">
         <f>IE!G32+IE!G33</f>
@@ -8721,7 +8724,7 @@
       </c>
       <c r="K8" s="7"/>
       <c r="L8" s="30" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="O8" s="159">
         <f>SUM(O4:O7)</f>
@@ -8747,10 +8750,10 @@
         <v>249</v>
       </c>
       <c r="K9" s="7" t="s">
+        <v>399</v>
+      </c>
+      <c r="L9" t="s">
         <v>400</v>
-      </c>
-      <c r="L9" t="s">
-        <v>401</v>
       </c>
       <c r="O9" s="160">
         <v>0</v>
@@ -8759,7 +8762,7 @@
     <row r="10" spans="1:15" x14ac:dyDescent="0.3">
       <c r="K10" s="7"/>
       <c r="L10" s="30" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="O10" s="159">
         <f>O8-O9</f>
@@ -8782,7 +8785,7 @@
       </c>
       <c r="K11" s="7"/>
       <c r="L11" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="N11" s="161">
         <v>0.1</v>
@@ -8811,7 +8814,7 @@
       </c>
       <c r="K12" s="7"/>
       <c r="L12" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="N12" s="161">
         <v>0.2</v>
@@ -8823,7 +8826,7 @@
     <row r="13" spans="1:15" x14ac:dyDescent="0.3">
       <c r="K13" s="7"/>
       <c r="L13" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="N13" s="161">
         <v>0.3</v>
@@ -8836,7 +8839,7 @@
     <row r="14" spans="1:15" x14ac:dyDescent="0.3">
       <c r="K14" s="7"/>
       <c r="L14" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="O14" s="159">
         <f>SUM(O11:O13)</f>
@@ -8848,10 +8851,10 @@
         <v>250</v>
       </c>
       <c r="K15" s="7" t="s">
+        <v>406</v>
+      </c>
+      <c r="L15" t="s">
         <v>407</v>
-      </c>
-      <c r="L15" t="s">
-        <v>408</v>
       </c>
       <c r="N15" s="161">
         <v>0.04</v>
@@ -8879,7 +8882,7 @@
       </c>
       <c r="K16" s="7"/>
       <c r="L16" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="O16" s="165">
         <f>SUM(O14:O15)</f>
@@ -8906,7 +8909,7 @@
       </c>
       <c r="K17" s="7"/>
       <c r="L17" s="162" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="O17" s="163">
         <f>ROUND(O16,-2)</f>
@@ -8987,7 +8990,7 @@
         <v>248</v>
       </c>
       <c r="Q24" s="136" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="R24" s="136" t="s">
         <v>248</v>
@@ -9008,7 +9011,7 @@
         <v>39777</v>
       </c>
       <c r="Q25" s="1" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="R25" s="167">
         <v>43053</v>
@@ -9033,7 +9036,7 @@
         <v>249</v>
       </c>
       <c r="Q26" s="1" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="R26" s="168">
         <v>73780</v>
@@ -9041,7 +9044,7 @@
     </row>
     <row r="27" spans="1:18" x14ac:dyDescent="0.3">
       <c r="Q27" s="1" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="R27" s="169">
         <v>79252</v>
@@ -9064,7 +9067,7 @@
         <v>248</v>
       </c>
       <c r="Q28" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="R28" s="170">
         <f>-IE!I41</f>
@@ -9086,7 +9089,7 @@
         <v>6000</v>
       </c>
       <c r="Q29" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="R29" s="170">
         <f>-IE!I50</f>
@@ -9112,13 +9115,13 @@
         <v>249</v>
       </c>
       <c r="G30" t="s">
+        <v>320</v>
+      </c>
+      <c r="H30" t="s">
         <v>321</v>
       </c>
-      <c r="H30" t="s">
-        <v>322</v>
-      </c>
       <c r="Q30" s="1" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="R30" s="170">
         <f>-IE!I52</f>
@@ -9166,16 +9169,16 @@
         <v>0</v>
       </c>
       <c r="G33" t="s">
+        <v>322</v>
+      </c>
+      <c r="H33" t="s">
         <v>323</v>
-      </c>
-      <c r="H33" t="s">
-        <v>324</v>
       </c>
       <c r="R33">
         <v>203</v>
       </c>
       <c r="S33" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="34" spans="2:19" x14ac:dyDescent="0.3">
@@ -9200,7 +9203,7 @@
         <v>1201</v>
       </c>
       <c r="S34" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="35" spans="2:19" x14ac:dyDescent="0.3">
@@ -9208,7 +9211,7 @@
         <v>1702</v>
       </c>
       <c r="S35" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="36" spans="2:19" x14ac:dyDescent="0.3">
@@ -9216,7 +9219,7 @@
         <v>2204</v>
       </c>
       <c r="S36" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
   </sheetData>
@@ -9246,7 +9249,7 @@
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A1" s="367" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="B1" s="367"/>
       <c r="C1" s="367"/>
@@ -9261,37 +9264,37 @@
     </row>
     <row r="2" spans="1:12" s="178" customFormat="1" ht="85.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="177" t="s">
+        <v>437</v>
+      </c>
+      <c r="B2" s="177" t="s">
+        <v>419</v>
+      </c>
+      <c r="C2" s="177" t="s">
+        <v>420</v>
+      </c>
+      <c r="D2" s="177" t="s">
+        <v>436</v>
+      </c>
+      <c r="E2" s="177" t="s">
+        <v>421</v>
+      </c>
+      <c r="F2" s="177" t="s">
+        <v>422</v>
+      </c>
+      <c r="G2" s="177" t="s">
+        <v>433</v>
+      </c>
+      <c r="H2" s="179" t="s">
+        <v>440</v>
+      </c>
+      <c r="I2" s="177" t="s">
         <v>438</v>
       </c>
-      <c r="B2" s="177" t="s">
-        <v>420</v>
-      </c>
-      <c r="C2" s="177" t="s">
-        <v>421</v>
-      </c>
-      <c r="D2" s="177" t="s">
-        <v>437</v>
-      </c>
-      <c r="E2" s="177" t="s">
-        <v>422</v>
-      </c>
-      <c r="F2" s="177" t="s">
-        <v>423</v>
-      </c>
-      <c r="G2" s="177" t="s">
+      <c r="J2" s="177" t="s">
+        <v>435</v>
+      </c>
+      <c r="K2" s="177" t="s">
         <v>434</v>
-      </c>
-      <c r="H2" s="179" t="s">
-        <v>441</v>
-      </c>
-      <c r="I2" s="177" t="s">
-        <v>439</v>
-      </c>
-      <c r="J2" s="177" t="s">
-        <v>436</v>
-      </c>
-      <c r="K2" s="177" t="s">
-        <v>435</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.3">
@@ -9302,10 +9305,10 @@
         <v>140</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="D3" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="E3" s="33">
         <v>43600</v>
@@ -9340,7 +9343,7 @@
         <v>140</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="D4" t="s">
         <v>202</v>
@@ -9378,7 +9381,7 @@
         <v>140</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D5" t="s">
         <v>201</v>
@@ -9416,7 +9419,7 @@
         <v>140</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="D6" t="s">
         <v>200</v>
@@ -9454,7 +9457,7 @@
         <v>140</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="D7" t="s">
         <v>269</v>
@@ -9492,7 +9495,7 @@
         <v>140</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="D8" t="s">
         <v>120</v>
@@ -9530,7 +9533,7 @@
         <v>140</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="D9" t="s">
         <v>139</v>
@@ -9568,7 +9571,7 @@
         <v>140</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="D10" t="s">
         <v>270</v>
@@ -9606,7 +9609,7 @@
         <v>140</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="D11" t="s">
         <v>271</v>
@@ -9644,7 +9647,7 @@
         <v>140</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="D12" t="s">
         <v>199</v>
@@ -9674,7 +9677,7 @@
         <v>0</v>
       </c>
       <c r="L12" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.3">
@@ -9685,7 +9688,7 @@
         <v>140</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="D13" t="s">
         <v>198</v>
@@ -9723,7 +9726,7 @@
         <v>140</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="D14" t="s">
         <v>197</v>
@@ -9761,7 +9764,7 @@
         <v>140</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="D15" t="s">
         <v>196</v>
@@ -9799,7 +9802,7 @@
         <v>140</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="D16" t="s">
         <v>195</v>
@@ -9837,7 +9840,7 @@
         <v>140</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="D17" t="s">
         <v>194</v>
@@ -9875,7 +9878,7 @@
         <v>140</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="D18" t="s">
         <v>193</v>
@@ -9913,7 +9916,7 @@
         <v>140</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="D19" t="s">
         <v>192</v>
@@ -9951,7 +9954,7 @@
         <v>140</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="D20" t="s">
         <v>191</v>
@@ -9989,7 +9992,7 @@
         <v>140</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="D21" t="s">
         <v>190</v>
@@ -10027,10 +10030,10 @@
         <v>140</v>
       </c>
       <c r="C22" s="4" t="s">
+        <v>351</v>
+      </c>
+      <c r="D22" t="s">
         <v>352</v>
-      </c>
-      <c r="D22" t="s">
-        <v>353</v>
       </c>
       <c r="E22" s="33">
         <v>43600</v>
@@ -10065,10 +10068,10 @@
         <v>140</v>
       </c>
       <c r="C23" s="4" t="s">
+        <v>353</v>
+      </c>
+      <c r="D23" t="s">
         <v>354</v>
-      </c>
-      <c r="D23" t="s">
-        <v>355</v>
       </c>
       <c r="E23" s="33">
         <v>54616</v>
@@ -10103,7 +10106,7 @@
         <v>140</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="D24" t="s">
         <v>38</v>
@@ -10141,7 +10144,7 @@
         <v>140</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="D25" t="s">
         <v>188</v>
@@ -10179,7 +10182,7 @@
         <v>140</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="D26" t="s">
         <v>187</v>
@@ -10217,10 +10220,10 @@
         <v>140</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="D27" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="E27" s="33">
         <v>54616</v>
@@ -10255,7 +10258,7 @@
         <v>140</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="D28" t="s">
         <v>117</v>
@@ -10293,7 +10296,7 @@
         <v>140</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="D29" t="s">
         <v>186</v>
@@ -10331,7 +10334,7 @@
         <v>140</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="D30" t="s">
         <v>185</v>
@@ -10369,7 +10372,7 @@
         <v>140</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="D31" t="s">
         <v>184</v>
@@ -10407,7 +10410,7 @@
         <v>140</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="D32" t="s">
         <v>203</v>
@@ -10446,7 +10449,7 @@
         <v>140</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="D33" t="s">
         <v>121</v>
@@ -10485,7 +10488,7 @@
         <v>140</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="D34" t="s">
         <v>183</v>
@@ -10523,7 +10526,7 @@
         <v>140</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="D35" t="s">
         <v>182</v>
@@ -10561,7 +10564,7 @@
         <v>140</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="D36" t="s">
         <v>181</v>
@@ -10599,7 +10602,7 @@
         <v>140</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="D37" t="s">
         <v>180</v>
@@ -10637,7 +10640,7 @@
         <v>140</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="D38" t="s">
         <v>179</v>
@@ -11364,7 +11367,7 @@
         <v>1403</v>
       </c>
       <c r="D57" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="E57" s="33">
         <v>43600</v>
@@ -11516,7 +11519,7 @@
         <v>1503</v>
       </c>
       <c r="D61" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="E61" s="33">
         <v>43600</v>
@@ -12278,7 +12281,7 @@
         <v>2004</v>
       </c>
       <c r="D81" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="E81" s="33">
         <v>54616</v>
@@ -12660,7 +12663,7 @@
         <v>2302</v>
       </c>
       <c r="D91" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="E91" s="33">
         <v>43600</v>
@@ -12771,10 +12774,10 @@
       <c r="C94" s="334"/>
       <c r="D94" s="334"/>
       <c r="E94" s="133" t="s">
+        <v>431</v>
+      </c>
+      <c r="F94" s="133" t="s">
         <v>432</v>
-      </c>
-      <c r="F94" s="133" t="s">
-        <v>433</v>
       </c>
       <c r="G94" s="133"/>
       <c r="H94" s="181">
@@ -12800,7 +12803,7 @@
         <v>5450</v>
       </c>
       <c r="L95" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
     </row>
     <row r="96" spans="1:12" x14ac:dyDescent="0.3">
